--- a/GroceryApplication/src/test/resources/TestDataSample.xlsx
+++ b/GroceryApplication/src/test/resources/TestDataSample.xlsx
@@ -4,16 +4,19 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java program files\GroceryApplication\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aby Philip\git\Groceryapp\GroceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
     <sheet name="managenewspage" sheetId="2" r:id="rId2"/>
     <sheet name="adminuser" sheetId="3" r:id="rId3"/>
+    <sheet name="managecontact" sheetId="4" r:id="rId4"/>
+    <sheet name="managefooter" sheetId="5" r:id="rId5"/>
+    <sheet name="managecategory" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr/>
 </workbook>
@@ -50,6 +53,39 @@
   </si>
   <si>
     <t>cavil</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>delivery time</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> delivery charge limit</t>
+  </si>
+  <si>
+    <t>gfbgh@gmail</t>
+  </si>
+  <si>
+    <t>tripunithura</t>
+  </si>
+  <si>
+    <t>india</t>
+  </si>
+  <si>
+    <t>hvvf@gmail</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>vegetabless</t>
   </si>
 </sst>
 </file>
@@ -91,10 +127,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,4 +526,108 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.85547" customWidth="1"/>
+    <col min="2" max="2" width="17.85547" customWidth="1"/>
+    <col min="3" max="3" width="12.14063" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="22.42578" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <v>12345678910</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="12.42578" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>12345678910</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.85547" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>